--- a/tests/testdata/excel/フォルダ/[角括弧]/角括弧フォルダ内.xlsx
+++ b/tests/testdata/excel/フォルダ/[角括弧]/角括弧フォルダ内.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{575F2E24-B47A-401F-9451-3850A1FA9437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{848DBD82-9DDC-48ED-BB17-D9A26F91004C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{64E8EBBA-7176-444E-B3BE-40A283224951}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{9648A792-7788-4EF9-A9D2-3F6249248674}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31936325-D4A4-4769-B945-6C8F4B678684}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22FD2590-1155-45EF-B687-8D21F0A7951A}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/フォルダ/[角括弧]/角括弧フォルダ内.xlsx
+++ b/tests/testdata/excel/フォルダ/[角括弧]/角括弧フォルダ内.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{848DBD82-9DDC-48ED-BB17-D9A26F91004C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB056658-E84B-449F-B464-453E26D432AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{9648A792-7788-4EF9-A9D2-3F6249248674}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{CD7C3C10-F875-4DF2-BE6D-F1F92ECB64F3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22FD2590-1155-45EF-B687-8D21F0A7951A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EACB75EB-0AF2-4234-A893-68F171741112}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
